--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>69.48982544759018</v>
+        <v>11.2920966352334</v>
       </c>
       <c r="D2" t="n">
-        <v>70.00602814379423</v>
+        <v>11.37597957336656</v>
       </c>
       <c r="E2" t="n">
-        <v>16.22538650846561</v>
+        <v>2.636625307625661</v>
       </c>
       <c r="F2" t="n">
-        <v>16.4805198703272</v>
+        <v>2.67808447892817</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>77.03316934114798</v>
+        <v>12.51789001793655</v>
       </c>
       <c r="D3" t="n">
-        <v>77.58259775729992</v>
+        <v>12.60717213556124</v>
       </c>
       <c r="E3" t="n">
-        <v>16.22538650846561</v>
+        <v>2.636625307625661</v>
       </c>
       <c r="F3" t="n">
-        <v>16.4805198703272</v>
+        <v>2.67808447892817</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.72142980117704</v>
+        <v>8.729732342691269</v>
       </c>
       <c r="D4" t="n">
-        <v>54.17054333444388</v>
+        <v>8.80271329184713</v>
       </c>
       <c r="E4" t="n">
-        <v>16.22538650846561</v>
+        <v>2.636625307625661</v>
       </c>
       <c r="F4" t="n">
-        <v>16.4805198703272</v>
+        <v>2.67808447892817</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>57.14080748936161</v>
+        <v>9.285381217021261</v>
       </c>
       <c r="D5" t="n">
-        <v>57.69854406620232</v>
+        <v>9.376013410757878</v>
       </c>
       <c r="E5" t="n">
-        <v>16.22538650846561</v>
+        <v>2.636625307625661</v>
       </c>
       <c r="F5" t="n">
-        <v>16.4805198703272</v>
+        <v>2.67808447892817</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>53.58703559589538</v>
+        <v>8.707893284333</v>
       </c>
       <c r="D6" t="n">
-        <v>54.14227914996049</v>
+        <v>8.79812036186858</v>
       </c>
       <c r="E6" t="n">
-        <v>16.22538650846561</v>
+        <v>2.636625307625661</v>
       </c>
       <c r="F6" t="n">
-        <v>16.4805198703272</v>
+        <v>2.67808447892817</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.67682135291465</v>
+        <v>4.984983469848632</v>
       </c>
       <c r="D7" t="n">
-        <v>31.21354767573935</v>
+        <v>5.072201497307645</v>
       </c>
       <c r="E7" t="n">
-        <v>16.22538650846561</v>
+        <v>2.636625307625661</v>
       </c>
       <c r="F7" t="n">
-        <v>16.4805198703272</v>
+        <v>2.67808447892817</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.52106043839608</v>
+        <v>6.747172321239363</v>
       </c>
       <c r="D8" t="n">
-        <v>42.03884991663586</v>
+        <v>6.831313111453328</v>
       </c>
       <c r="E8" t="n">
-        <v>16.22538650846561</v>
+        <v>2.636625307625661</v>
       </c>
       <c r="F8" t="n">
-        <v>16.4805198703272</v>
+        <v>2.67808447892817</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.22060140208075</v>
+        <v>5.560847727838123</v>
       </c>
       <c r="D9" t="n">
-        <v>34.66008524022582</v>
+        <v>5.632263851536695</v>
       </c>
       <c r="E9" t="n">
-        <v>16.22538650846561</v>
+        <v>2.636625307625661</v>
       </c>
       <c r="F9" t="n">
-        <v>16.4805198703272</v>
+        <v>2.67808447892817</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>16.53651257855373</v>
+        <v>2.68718329401498</v>
       </c>
       <c r="D10" t="n">
-        <v>17.02762118228764</v>
+        <v>2.766988442121742</v>
       </c>
       <c r="E10" t="n">
-        <v>16.22538650846561</v>
+        <v>2.636625307625661</v>
       </c>
       <c r="F10" t="n">
-        <v>16.4805198703272</v>
+        <v>2.67808447892817</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>37.96181826972886</v>
+        <v>6.16879546883094</v>
       </c>
       <c r="D11" t="n">
-        <v>37.51524770225666</v>
+        <v>6.096227751616707</v>
       </c>
       <c r="E11" t="n">
-        <v>16.22538650846561</v>
+        <v>2.636625307625661</v>
       </c>
       <c r="F11" t="n">
-        <v>16.4805198703272</v>
+        <v>2.67808447892817</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>25.82553653943102</v>
+        <v>4.196649687657541</v>
       </c>
       <c r="D12" t="n">
-        <v>25.40047581336934</v>
+        <v>4.127577319672517</v>
       </c>
       <c r="E12" t="n">
-        <v>16.22538650846561</v>
+        <v>2.636625307625661</v>
       </c>
       <c r="F12" t="n">
-        <v>16.4805198703272</v>
+        <v>2.67808447892817</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>20.43911240560547</v>
+        <v>3.321355765910889</v>
       </c>
       <c r="D13" t="n">
-        <v>19.88716236266296</v>
+        <v>3.231663883932732</v>
       </c>
       <c r="E13" t="n">
-        <v>16.22538650846561</v>
+        <v>2.636625307625661</v>
       </c>
       <c r="F13" t="n">
-        <v>16.4805198703272</v>
+        <v>2.67808447892817</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>41.47006132648675</v>
+        <v>6.738884965554097</v>
       </c>
       <c r="D14" t="n">
-        <v>41.66853428671041</v>
+        <v>6.771136821590442</v>
       </c>
       <c r="E14" t="n">
-        <v>16.22538650846561</v>
+        <v>2.636625307625661</v>
       </c>
       <c r="F14" t="n">
-        <v>16.4805198703272</v>
+        <v>2.67808447892817</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>35.75829004915289</v>
+        <v>5.810722132987345</v>
       </c>
       <c r="D15" t="n">
-        <v>35.21372733436227</v>
+        <v>5.722230691833869</v>
       </c>
       <c r="E15" t="n">
-        <v>16.22538650846561</v>
+        <v>2.636625307625661</v>
       </c>
       <c r="F15" t="n">
-        <v>16.4805198703272</v>
+        <v>2.67808447892817</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>28.85460164474188</v>
+        <v>4.688872767270556</v>
       </c>
       <c r="D16" t="n">
-        <v>28.8167616212082</v>
+        <v>4.682723763446333</v>
       </c>
       <c r="E16" t="n">
-        <v>16.22538650846561</v>
+        <v>2.636625307625661</v>
       </c>
       <c r="F16" t="n">
-        <v>16.4805198703272</v>
+        <v>2.67808447892817</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>27.56553673746674</v>
+        <v>4.479399719838345</v>
       </c>
       <c r="D17" t="n">
-        <v>27.03326055768157</v>
+        <v>4.392904840623254</v>
       </c>
       <c r="E17" t="n">
-        <v>16.22538650846561</v>
+        <v>2.636625307625661</v>
       </c>
       <c r="F17" t="n">
-        <v>16.4805198703272</v>
+        <v>2.67808447892817</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>36.54770472811559</v>
+        <v>5.939002018318783</v>
       </c>
       <c r="D18" t="n">
-        <v>35.9895924415586</v>
+        <v>5.848308771753272</v>
       </c>
       <c r="E18" t="n">
-        <v>16.22538650846561</v>
+        <v>2.636625307625661</v>
       </c>
       <c r="F18" t="n">
-        <v>16.4805198703272</v>
+        <v>2.67808447892817</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
